--- a/p6_deployment/data/usa/missing/data_understanding/all/df_match_miss.xlsx
+++ b/p6_deployment/data/usa/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL110"/>
+  <dimension ref="A1:BL134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23594,15 +23594,11 @@
           <t>3 481</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G109" t="n">
+        <v>3</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -23634,179 +23630,111 @@
           <t>61%</t>
         </is>
       </c>
-      <c r="O109" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P109" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Q109" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T109" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U109" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V109" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="O109" t="n">
+        <v>10</v>
+      </c>
+      <c r="P109" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>5</v>
+      </c>
+      <c r="R109" t="n">
+        <v>1</v>
+      </c>
+      <c r="S109" t="n">
+        <v>2</v>
+      </c>
+      <c r="T109" t="n">
+        <v>3</v>
+      </c>
+      <c r="U109" t="n">
+        <v>3</v>
+      </c>
+      <c r="V109" t="n">
+        <v>3</v>
       </c>
       <c r="W109" t="inlineStr"/>
       <c r="X109" t="inlineStr"/>
-      <c r="Y109" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA109" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y109" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA109" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB109" t="n">
+        <v>0</v>
       </c>
       <c r="AC109" t="inlineStr"/>
       <c r="AD109" t="inlineStr"/>
-      <c r="AE109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF109" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG109" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AI109" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AJ109" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AK109" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="AL109" t="inlineStr">
-        <is>
-          <t>507</t>
-        </is>
-      </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>409</t>
-        </is>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AP109" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AQ109" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="AS109" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="AT109" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="AU109" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AV109" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AW109" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AX109" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AY109" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AZ109" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="AE109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF109" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG109" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH109" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI109" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ109" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK109" t="n">
+        <v>322</v>
+      </c>
+      <c r="AL109" t="n">
+        <v>507</v>
+      </c>
+      <c r="AM109" t="n">
+        <v>242</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>409</v>
+      </c>
+      <c r="AO109" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP109" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ109" t="n">
+        <v>117</v>
+      </c>
+      <c r="AR109" t="n">
+        <v>113</v>
+      </c>
+      <c r="AS109" t="n">
+        <v>51</v>
+      </c>
+      <c r="AT109" t="n">
+        <v>40</v>
+      </c>
+      <c r="AU109" t="n">
+        <v>18</v>
+      </c>
+      <c r="AV109" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW109" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX109" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY109" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ109" t="n">
+        <v>7</v>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
@@ -23837,20 +23765,14 @@
       <c r="BG109" t="n">
         <v>0</v>
       </c>
-      <c r="BH109" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="BI109" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BJ109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="BH109" t="n">
+        <v>2024</v>
+      </c>
+      <c r="BI109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ109" t="n">
+        <v>1</v>
       </c>
       <c r="BK109" t="inlineStr"/>
       <c r="BL109" t="inlineStr"/>
@@ -23888,15 +23810,11 @@
           <t>6 244</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H110" t="n">
+        <v>2</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -23928,179 +23846,111 @@
           <t>49%</t>
         </is>
       </c>
-      <c r="O110" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="P110" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q110" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R110" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T110" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U110" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V110" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="O110" t="n">
+        <v>6</v>
+      </c>
+      <c r="P110" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>1</v>
+      </c>
+      <c r="R110" t="n">
+        <v>7</v>
+      </c>
+      <c r="S110" t="n">
+        <v>4</v>
+      </c>
+      <c r="T110" t="n">
+        <v>3</v>
+      </c>
+      <c r="U110" t="n">
+        <v>1</v>
+      </c>
+      <c r="V110" t="n">
+        <v>5</v>
       </c>
       <c r="W110" t="inlineStr"/>
       <c r="X110" t="inlineStr"/>
-      <c r="Y110" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA110" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Y110" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA110" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB110" t="n">
+        <v>2</v>
       </c>
       <c r="AC110" t="inlineStr"/>
       <c r="AD110" t="inlineStr"/>
-      <c r="AE110" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AF110" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG110" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AI110" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
-      <c r="AL110" t="inlineStr">
-        <is>
-          <t>473</t>
-        </is>
-      </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>389</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AP110" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AQ110" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="AS110" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="AT110" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="AU110" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AV110" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AW110" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AY110" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AZ110" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AE110" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH110" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI110" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ110" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK110" t="n">
+        <v>468</v>
+      </c>
+      <c r="AL110" t="n">
+        <v>473</v>
+      </c>
+      <c r="AM110" t="n">
+        <v>381</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>389</v>
+      </c>
+      <c r="AO110" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP110" t="n">
+        <v>23</v>
+      </c>
+      <c r="AQ110" t="n">
+        <v>83</v>
+      </c>
+      <c r="AR110" t="n">
+        <v>81</v>
+      </c>
+      <c r="AS110" t="n">
+        <v>46</v>
+      </c>
+      <c r="AT110" t="n">
+        <v>59</v>
+      </c>
+      <c r="AU110" t="n">
+        <v>25</v>
+      </c>
+      <c r="AV110" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW110" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX110" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY110" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ110" t="n">
+        <v>4</v>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
@@ -24131,16 +23981,6818 @@
       <c r="BG110" t="n">
         <v>0</v>
       </c>
-      <c r="BH110" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="BH110" t="n">
+        <v>2024</v>
       </c>
       <c r="BI110" t="inlineStr"/>
       <c r="BJ110" t="inlineStr"/>
       <c r="BK110" t="inlineStr"/>
       <c r="BL110" t="inlineStr"/>
     </row>
+    <row r="111">
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>xbHaKGH7</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>29.06.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Penso C.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>BMO Stadium
+ (Los Angeles, CA)</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>22 000</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Colorado Rapids</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AD111" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF111" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AG111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="AL111" t="inlineStr">
+        <is>
+          <t>459</t>
+        </is>
+      </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="AN111" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr"/>
+      <c r="AP111" t="inlineStr"/>
+      <c r="AQ111" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="AT111" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="AU111" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AV111" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr"/>
+      <c r="BA111" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="BB111" t="inlineStr">
+        <is>
+          <t>cherundolo steve</t>
+        </is>
+      </c>
+      <c r="BC111" t="inlineStr">
+        <is>
+          <t>lAVQ9RGh</t>
+        </is>
+      </c>
+      <c r="BD111" t="inlineStr">
+        <is>
+          <t>armas chris</t>
+        </is>
+      </c>
+      <c r="BE111" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF111" t="n">
+        <v>1671</v>
+      </c>
+      <c r="BG111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH111" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BJ111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BK111" t="inlineStr"/>
+      <c r="BL111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>v3erq0f8</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>29.06.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Ford T.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Providence Park
+ (Portland, OR)</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>25 218</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Minnesota United</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr"/>
+      <c r="AJ112" t="inlineStr"/>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="AL112" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>531</t>
+        </is>
+      </c>
+      <c r="AN112" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr"/>
+      <c r="AP112" t="inlineStr"/>
+      <c r="AQ112" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AT112" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AV112" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr"/>
+      <c r="BA112" t="inlineStr">
+        <is>
+          <t>EqKWmJfM</t>
+        </is>
+      </c>
+      <c r="BB112" t="inlineStr">
+        <is>
+          <t>neville phil</t>
+        </is>
+      </c>
+      <c r="BC112" t="inlineStr">
+        <is>
+          <t>UFWZoX9L</t>
+        </is>
+      </c>
+      <c r="BD112" t="inlineStr">
+        <is>
+          <t>ramsay eric</t>
+        </is>
+      </c>
+      <c r="BE112" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF112" t="n">
+        <v>1671</v>
+      </c>
+      <c r="BG112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH112" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI112" t="inlineStr"/>
+      <c r="BJ112" t="inlineStr"/>
+      <c r="BK112" t="inlineStr"/>
+      <c r="BL112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>IgfnrK9E</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>29.06.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Gonzales G.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Stanford Stadium
+ (Stanford, CA)</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>50 424</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>40 844</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>San Jose Earthquakes</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Los Angeles Galaxy</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AD113" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AG113" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="AL113" t="inlineStr">
+        <is>
+          <t>589</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="AN113" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr"/>
+      <c r="AP113" t="inlineStr"/>
+      <c r="AQ113" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="AT113" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AV113" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr"/>
+      <c r="BA113" t="inlineStr">
+        <is>
+          <t>bFuhdIb3</t>
+        </is>
+      </c>
+      <c r="BB113" t="inlineStr">
+        <is>
+          <t>russell ian</t>
+        </is>
+      </c>
+      <c r="BC113" t="inlineStr">
+        <is>
+          <t>2PIEeC7j</t>
+        </is>
+      </c>
+      <c r="BD113" t="inlineStr">
+        <is>
+          <t>vanney greg</t>
+        </is>
+      </c>
+      <c r="BE113" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF113" t="n">
+        <v>1671</v>
+      </c>
+      <c r="BG113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH113" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI113" t="inlineStr"/>
+      <c r="BJ113" t="inlineStr"/>
+      <c r="BK113" t="inlineStr"/>
+      <c r="BL113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>nTbjsvPK</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>29.06.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Dickerson J.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Lumen Field
+ (Seattle, WA)</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>72 000</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Chicago Fire</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AD114" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="AL114" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="AN114" t="inlineStr">
+        <is>
+          <t>386</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr"/>
+      <c r="AP114" t="inlineStr"/>
+      <c r="AQ114" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AT114" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AU114" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AV114" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr"/>
+      <c r="BA114" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="BB114" t="inlineStr">
+        <is>
+          <t>schmetzer brian</t>
+        </is>
+      </c>
+      <c r="BC114" t="inlineStr">
+        <is>
+          <t>6LuGZiZI</t>
+        </is>
+      </c>
+      <c r="BD114" t="inlineStr">
+        <is>
+          <t>klopas frank</t>
+        </is>
+      </c>
+      <c r="BE114" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF114" t="n">
+        <v>1671</v>
+      </c>
+      <c r="BG114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH114" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI114" t="inlineStr"/>
+      <c r="BJ114" t="inlineStr"/>
+      <c r="BK114" t="inlineStr"/>
+      <c r="BL114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="inlineStr">
+        <is>
+          <t>YyTMIXGq</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>29.06.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Allatin M.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>BC Place
+ (Vancouver, BC)</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>54 405</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>24 662</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>St. Louis City</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AD115" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF115" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG115" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="AL115" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="AN115" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr"/>
+      <c r="AP115" t="inlineStr"/>
+      <c r="AQ115" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AT115" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AU115" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AV115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr"/>
+      <c r="BA115" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+      <c r="BB115" t="inlineStr">
+        <is>
+          <t>sartini vanni</t>
+        </is>
+      </c>
+      <c r="BC115" t="inlineStr">
+        <is>
+          <t>z9ZXDy6o</t>
+        </is>
+      </c>
+      <c r="BD115" t="inlineStr">
+        <is>
+          <t>carnell bradley</t>
+        </is>
+      </c>
+      <c r="BE115" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF115" t="n">
+        <v>1671</v>
+      </c>
+      <c r="BG115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH115" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI115" t="inlineStr"/>
+      <c r="BJ115" t="inlineStr"/>
+      <c r="BK115" t="inlineStr"/>
+      <c r="BL115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="inlineStr">
+        <is>
+          <t>zZKrObIr</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>29.06.2024 21:30</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Rivas V.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Toyota Stadium
+ (Frisco, TX)</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>20 500</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>19 096</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>FC Cincinnati</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AD116" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>447</t>
+        </is>
+      </c>
+      <c r="AL116" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="AN116" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr"/>
+      <c r="AP116" t="inlineStr"/>
+      <c r="AQ116" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="AT116" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AV116" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AW116" t="inlineStr"/>
+      <c r="AX116" t="inlineStr"/>
+      <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr"/>
+      <c r="BA116" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+      <c r="BB116" t="inlineStr">
+        <is>
+          <t>luccin peter</t>
+        </is>
+      </c>
+      <c r="BC116" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="BD116" t="inlineStr">
+        <is>
+          <t>noonan pat</t>
+        </is>
+      </c>
+      <c r="BE116" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF116" t="n">
+        <v>1671</v>
+      </c>
+      <c r="BG116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH116" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI116" t="inlineStr"/>
+      <c r="BJ116" t="inlineStr"/>
+      <c r="BK116" t="inlineStr"/>
+      <c r="BL116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t>hAFmNIXl</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>29.06.2024 21:30</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Lauziere P.
+ (Can)</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Shell Energy Stadium
+ (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>22 039</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>15 321</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Houston Dynamo</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AD117" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="AL117" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="AN117" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr"/>
+      <c r="AP117" t="inlineStr"/>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AT117" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AV117" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AW117" t="inlineStr"/>
+      <c r="AX117" t="inlineStr"/>
+      <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr"/>
+      <c r="BA117" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
+        </is>
+      </c>
+      <c r="BB117" t="inlineStr">
+        <is>
+          <t>olsen ben</t>
+        </is>
+      </c>
+      <c r="BC117" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
+        </is>
+      </c>
+      <c r="BD117" t="inlineStr">
+        <is>
+          <t>smith dean</t>
+        </is>
+      </c>
+      <c r="BE117" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1671</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH117" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI117" t="inlineStr"/>
+      <c r="BJ117" t="inlineStr"/>
+      <c r="BK117" t="inlineStr"/>
+      <c r="BL117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="inlineStr">
+        <is>
+          <t>QNDeLd21</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>29.06.2024 21:30</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Szpala L.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Geodis Park
+ (Nashville, TN)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>30 000</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>30 109</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Nashville SC</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Inter Miami</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="AL118" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>465</t>
+        </is>
+      </c>
+      <c r="AN118" t="inlineStr">
+        <is>
+          <t>423</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr"/>
+      <c r="AP118" t="inlineStr"/>
+      <c r="AQ118" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AT118" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AU118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AV118" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AW118" t="inlineStr"/>
+      <c r="AX118" t="inlineStr"/>
+      <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr"/>
+      <c r="BA118" t="inlineStr">
+        <is>
+          <t>EgT3xN3S</t>
+        </is>
+      </c>
+      <c r="BB118" t="inlineStr">
+        <is>
+          <t>munthali rumba</t>
+        </is>
+      </c>
+      <c r="BC118" t="inlineStr">
+        <is>
+          <t>6gpXy3vi</t>
+        </is>
+      </c>
+      <c r="BD118" t="inlineStr">
+        <is>
+          <t>martino gerardo</t>
+        </is>
+      </c>
+      <c r="BE118" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1671</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH118" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI118" t="inlineStr"/>
+      <c r="BJ118" t="inlineStr"/>
+      <c r="BK118" t="inlineStr"/>
+      <c r="BL118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>W0EiMxme</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>29.06.2024 21:30</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Dujic F.
+ (Can)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Children's Mercy Park
+ (Kansas City, KS)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>18 500</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>18 722</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Sporting Kansas City</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Austin FC</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AD119" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AE119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG119" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="AL119" t="inlineStr">
+        <is>
+          <t>384</t>
+        </is>
+      </c>
+      <c r="AM119" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="AN119" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr"/>
+      <c r="AP119" t="inlineStr"/>
+      <c r="AQ119" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="AT119" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AV119" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AW119" t="inlineStr"/>
+      <c r="AX119" t="inlineStr"/>
+      <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr"/>
+      <c r="BA119" t="inlineStr">
+        <is>
+          <t>jBBpU7Y0</t>
+        </is>
+      </c>
+      <c r="BB119" t="inlineStr">
+        <is>
+          <t>vermes peter</t>
+        </is>
+      </c>
+      <c r="BC119" t="inlineStr">
+        <is>
+          <t>KtuTuMN0</t>
+        </is>
+      </c>
+      <c r="BD119" t="inlineStr">
+        <is>
+          <t>wolff josh</t>
+        </is>
+      </c>
+      <c r="BE119" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>1671</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH119" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI119" t="inlineStr"/>
+      <c r="BJ119" t="inlineStr"/>
+      <c r="BK119" t="inlineStr"/>
+      <c r="BL119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="inlineStr">
+        <is>
+          <t>G0IRHiWk</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>29.06.2024 20:30</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>De Oliveira M.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz Stadium
+ (Atlanta, GA)</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>71 000</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>42 568</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Atlanta Utd</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Toronto FC</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AD120" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="AL120" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="AN120" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr"/>
+      <c r="AP120" t="inlineStr"/>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="AT120" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AV120" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr"/>
+      <c r="BA120" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+      <c r="BB120" t="inlineStr">
+        <is>
+          <t>valentino rob</t>
+        </is>
+      </c>
+      <c r="BC120" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+      <c r="BD120" t="inlineStr">
+        <is>
+          <t>herdman john</t>
+        </is>
+      </c>
+      <c r="BE120" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>1671</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH120" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI120" t="inlineStr"/>
+      <c r="BJ120" t="inlineStr"/>
+      <c r="BK120" t="inlineStr"/>
+      <c r="BL120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>fiHVGBod</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>29.06.2024 20:30</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Freemon J.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Saputo Stadium
+ (Montreal, QC)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>23 112</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>19 619</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>CF Montreal</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Philadelphia Union</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="AL121" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="AN121" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr"/>
+      <c r="AP121" t="inlineStr"/>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="AT121" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AV121" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr"/>
+      <c r="BA121" t="inlineStr">
+        <is>
+          <t>K4FYmLD9</t>
+        </is>
+      </c>
+      <c r="BB121" t="inlineStr">
+        <is>
+          <t>courtois laurent</t>
+        </is>
+      </c>
+      <c r="BC121" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="BD121" t="inlineStr">
+        <is>
+          <t>curtin jim</t>
+        </is>
+      </c>
+      <c r="BE121" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>1671</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH121" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI121" t="inlineStr"/>
+      <c r="BJ121" t="inlineStr"/>
+      <c r="BK121" t="inlineStr"/>
+      <c r="BL121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="inlineStr">
+        <is>
+          <t>4nbBt7Y9</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>29.06.2024 20:30</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Fierro R.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Gillette Stadium
+ (Foxborough, MA)</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>68 756</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>25 004</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>New England Revolution</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>Columbus Crew</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AD122" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="AL122" t="inlineStr">
+        <is>
+          <t>552</t>
+        </is>
+      </c>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="AN122" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr"/>
+      <c r="AP122" t="inlineStr"/>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AT122" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AV122" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr"/>
+      <c r="BA122" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+      <c r="BB122" t="inlineStr">
+        <is>
+          <t>porter caleb</t>
+        </is>
+      </c>
+      <c r="BC122" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="BD122" t="inlineStr">
+        <is>
+          <t>nancy wilfried</t>
+        </is>
+      </c>
+      <c r="BE122" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>1671</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH122" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI122" t="inlineStr"/>
+      <c r="BJ122" t="inlineStr"/>
+      <c r="BK122" t="inlineStr"/>
+      <c r="BL122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="inlineStr">
+        <is>
+          <t>b9cFuRmG</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>29.06.2024 20:30</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Badawi M.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Red Bull Arena
+ (Harrison, NJ)</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>25 000</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>18 315</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>New York Red Bulls</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>DC United</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>507</t>
+        </is>
+      </c>
+      <c r="AL123" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>434</t>
+        </is>
+      </c>
+      <c r="AN123" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr"/>
+      <c r="AP123" t="inlineStr"/>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="AT123" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AV123" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr"/>
+      <c r="BA123" t="inlineStr">
+        <is>
+          <t>rJ9D8rzj</t>
+        </is>
+      </c>
+      <c r="BB123" t="inlineStr">
+        <is>
+          <t>schwarz sandro</t>
+        </is>
+      </c>
+      <c r="BC123" t="inlineStr">
+        <is>
+          <t>nJ01AhXP</t>
+        </is>
+      </c>
+      <c r="BD123" t="inlineStr">
+        <is>
+          <t>lesesne troy</t>
+        </is>
+      </c>
+      <c r="BE123" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>1671</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH123" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BJ123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BK123" t="inlineStr"/>
+      <c r="BL123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="inlineStr">
+        <is>
+          <t>jqf7smJ3</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>28.06.2024 20:30</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Boiko S.
+ (Ukr)</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Yankee Stadium
+ (New York, NY)</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>54 251</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Orlando City</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AD124" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>599</t>
+        </is>
+      </c>
+      <c r="AL124" t="inlineStr">
+        <is>
+          <t>531</t>
+        </is>
+      </c>
+      <c r="AM124" t="inlineStr">
+        <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="AN124" t="inlineStr">
+        <is>
+          <t>435</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr"/>
+      <c r="AP124" t="inlineStr"/>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="AT124" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AV124" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr"/>
+      <c r="BA124" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+      <c r="BB124" t="inlineStr">
+        <is>
+          <t>cushing nicholas</t>
+        </is>
+      </c>
+      <c r="BC124" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="BD124" t="inlineStr">
+        <is>
+          <t>pareja oscar</t>
+        </is>
+      </c>
+      <c r="BE124" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>1671</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH124" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI124" t="inlineStr"/>
+      <c r="BJ124" t="inlineStr"/>
+      <c r="BK124" t="inlineStr"/>
+      <c r="BL124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t>63KkwxaD</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>30.06.2024 00:00</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Hassan M.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Heart Health Park
+ (Sacramento, CA)</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>11 569</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>9 249</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>z3BFwb83</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Sacramento Republic</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Ew2P6PKC</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Hartford Athletic</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr"/>
+      <c r="V125" t="inlineStr"/>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr"/>
+      <c r="AL125" t="inlineStr"/>
+      <c r="AM125" t="inlineStr"/>
+      <c r="AN125" t="inlineStr"/>
+      <c r="AO125" t="inlineStr"/>
+      <c r="AP125" t="inlineStr"/>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AT125" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="AU125" t="inlineStr"/>
+      <c r="AV125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr"/>
+      <c r="AX125" t="inlineStr"/>
+      <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr"/>
+      <c r="BA125" t="inlineStr">
+        <is>
+          <t>URfp4iBR</t>
+        </is>
+      </c>
+      <c r="BB125" t="inlineStr">
+        <is>
+          <t>briggs mark</t>
+        </is>
+      </c>
+      <c r="BC125" t="inlineStr">
+        <is>
+          <t>xYHj0Fat</t>
+        </is>
+      </c>
+      <c r="BD125" t="inlineStr">
+        <is>
+          <t>burke brendan</t>
+        </is>
+      </c>
+      <c r="BE125" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>1673</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH125" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI125" t="inlineStr"/>
+      <c r="BJ125" t="inlineStr"/>
+      <c r="BK125" t="inlineStr"/>
+      <c r="BL125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>xOSYtKal</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>29.06.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Griggs J.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Cashman Field
+ (Las Vegas, NV)</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>12 500</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>1 893</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>vVWDE67k</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Las Vegas Lights</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>trYG3CIh</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Pittsburgh</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr"/>
+      <c r="X126" t="inlineStr"/>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr"/>
+      <c r="AD126" t="inlineStr"/>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="AL126" t="inlineStr">
+        <is>
+          <t>447</t>
+        </is>
+      </c>
+      <c r="AM126" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="AN126" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AP126" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AT126" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AV126" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BA126" t="inlineStr">
+        <is>
+          <t>zDeq7OqE</t>
+        </is>
+      </c>
+      <c r="BB126" t="inlineStr">
+        <is>
+          <t>sanchez dennis</t>
+        </is>
+      </c>
+      <c r="BC126" t="inlineStr">
+        <is>
+          <t>j7eIjow4</t>
+        </is>
+      </c>
+      <c r="BD126" t="inlineStr">
+        <is>
+          <t>lilley bob</t>
+        </is>
+      </c>
+      <c r="BE126" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1673</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH126" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI126" t="inlineStr"/>
+      <c r="BJ126" t="inlineStr"/>
+      <c r="BK126" t="inlineStr"/>
+      <c r="BL126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="inlineStr">
+        <is>
+          <t>SCLovIq7</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>29.06.2024 23:00</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Garcia E.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Championship Soccer Stadium
+ (Irvine, CA)</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>5 000</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>llkqyHYq</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Orange County SC</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>zLYVwGMm</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Oakland Roots</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr"/>
+      <c r="X127" t="inlineStr"/>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr"/>
+      <c r="AD127" t="inlineStr"/>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="AL127" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="AN127" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="AT127" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AV127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BA127" t="inlineStr">
+        <is>
+          <t>pKAODsPO</t>
+        </is>
+      </c>
+      <c r="BB127" t="inlineStr">
+        <is>
+          <t>hardyman paul</t>
+        </is>
+      </c>
+      <c r="BC127" t="inlineStr">
+        <is>
+          <t>A7iCSGMH</t>
+        </is>
+      </c>
+      <c r="BD127" t="inlineStr">
+        <is>
+          <t>glinton gavin</t>
+        </is>
+      </c>
+      <c r="BE127" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>1673</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH127" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI127" t="inlineStr"/>
+      <c r="BJ127" t="inlineStr"/>
+      <c r="BK127" t="inlineStr"/>
+      <c r="BL127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="inlineStr">
+        <is>
+          <t>bXTUs0pr</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>29.06.2024 22:00</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Hernandez L.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Weidner Field
+ (Colorado Springs, CO)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>8 000</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>8 023</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>rmLxuq9b</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Colorado Springs</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>0vY9Fnhq</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Monterey Bay</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr"/>
+      <c r="X128" t="inlineStr"/>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr"/>
+      <c r="AD128" t="inlineStr"/>
+      <c r="AE128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG128" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="AL128" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="AM128" t="inlineStr">
+        <is>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="AN128" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AP128" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AQ128" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="AR128" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="AT128" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AU128" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AV128" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BA128" t="inlineStr">
+        <is>
+          <t>6V8Ndys8</t>
+        </is>
+      </c>
+      <c r="BB128" t="inlineStr">
+        <is>
+          <t>chambers james</t>
+        </is>
+      </c>
+      <c r="BC128" t="inlineStr">
+        <is>
+          <t>xKVirYma</t>
+        </is>
+      </c>
+      <c r="BD128" t="inlineStr">
+        <is>
+          <t>yallop frank</t>
+        </is>
+      </c>
+      <c r="BE128" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>1673</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH128" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI128" t="inlineStr"/>
+      <c r="BJ128" t="inlineStr"/>
+      <c r="BK128" t="inlineStr"/>
+      <c r="BL128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="inlineStr">
+        <is>
+          <t>6eQQ1LyE</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>29.06.2024 22:00</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Corrigan M.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Toyota Field
+ (San Antonio, TX)</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>8 296</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>6 625</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>8njPmvTl</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>dI5p0xzH</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>New Mexico</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr"/>
+      <c r="X129" t="inlineStr"/>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr"/>
+      <c r="AD129" t="inlineStr"/>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>437</t>
+        </is>
+      </c>
+      <c r="AL129" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="AM129" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="AN129" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AP129" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AQ129" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="AR129" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="AT129" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AV129" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BA129" t="inlineStr">
+        <is>
+          <t>6X9nrWKc</t>
+        </is>
+      </c>
+      <c r="BB129" t="inlineStr">
+        <is>
+          <t>marcina alen</t>
+        </is>
+      </c>
+      <c r="BC129" t="inlineStr">
+        <is>
+          <t>Cf83muss</t>
+        </is>
+      </c>
+      <c r="BD129" t="inlineStr">
+        <is>
+          <t>quill eric</t>
+        </is>
+      </c>
+      <c r="BE129" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1673</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH129" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BJ129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BK129" t="inlineStr"/>
+      <c r="BL129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="inlineStr">
+        <is>
+          <t>WO01aSFF</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>29.06.2024 20:30</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Encarnación J.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Protective Stadium
+ (Birmingham, AL)</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>47 100</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>rysqEtSu</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Birmingham</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>nRGIlQ2T</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Louisville City</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr"/>
+      <c r="X130" t="inlineStr"/>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr"/>
+      <c r="AD130" t="inlineStr"/>
+      <c r="AE130" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF130" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG130" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="AL130" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="AM130" t="inlineStr">
+        <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="AN130" t="inlineStr">
+        <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AP130" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="AR130" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AT130" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AU130" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AV130" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BA130" t="inlineStr">
+        <is>
+          <t>v7f8zS64</t>
+        </is>
+      </c>
+      <c r="BB130" t="inlineStr">
+        <is>
+          <t>soehn tom</t>
+        </is>
+      </c>
+      <c r="BC130" t="inlineStr">
+        <is>
+          <t>IorPEfz8</t>
+        </is>
+      </c>
+      <c r="BD130" t="inlineStr">
+        <is>
+          <t>cruz danny</t>
+        </is>
+      </c>
+      <c r="BE130" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>1673</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH130" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI130" t="inlineStr"/>
+      <c r="BJ130" t="inlineStr"/>
+      <c r="BK130" t="inlineStr"/>
+      <c r="BL130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="inlineStr">
+        <is>
+          <t>KnIwtvFf</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>29.06.2024 20:30</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Arroyo L.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Segra Field
+ (Leesburg, VA)</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>5 000</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>3 076</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>faQG6GQT</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Loudoun</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>AohGC74A</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Tampa Bay</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr"/>
+      <c r="X131" t="inlineStr"/>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr"/>
+      <c r="AD131" t="inlineStr"/>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AG131" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="AL131" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="AM131" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="AN131" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AP131" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="AT131" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AV131" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BA131" t="inlineStr">
+        <is>
+          <t>tvIcCmLN</t>
+        </is>
+      </c>
+      <c r="BB131" t="inlineStr">
+        <is>
+          <t>martin ryan</t>
+        </is>
+      </c>
+      <c r="BC131" t="inlineStr">
+        <is>
+          <t>SUJLjQfn</t>
+        </is>
+      </c>
+      <c r="BD131" t="inlineStr">
+        <is>
+          <t>neilson robbie</t>
+        </is>
+      </c>
+      <c r="BE131" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>1673</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH131" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI131" t="inlineStr"/>
+      <c r="BJ131" t="inlineStr"/>
+      <c r="BK131" t="inlineStr"/>
+      <c r="BL131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="inlineStr">
+        <is>
+          <t>YkMsubU0</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>29.06.2024 20:00</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Nichols A.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Riccardo Silva Stadium
+ (Miami, FL)</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>20 000</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>1 077</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>UJTiXUTf</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Miami FC</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>dAoaDOc7</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>Detroit</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr"/>
+      <c r="X132" t="inlineStr"/>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr"/>
+      <c r="AD132" t="inlineStr"/>
+      <c r="AE132" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF132" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG132" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="AL132" t="inlineStr">
+        <is>
+          <t>558</t>
+        </is>
+      </c>
+      <c r="AM132" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="AN132" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AP132" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AQ132" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="AR132" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="AT132" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="AU132" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AV132" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BA132" t="inlineStr">
+        <is>
+          <t>zVUAOJSG</t>
+        </is>
+      </c>
+      <c r="BB132" t="inlineStr">
+        <is>
+          <t>nocerino antonio</t>
+        </is>
+      </c>
+      <c r="BC132" t="inlineStr">
+        <is>
+          <t>lKNscApp</t>
+        </is>
+      </c>
+      <c r="BD132" t="inlineStr">
+        <is>
+          <t>dichio danny</t>
+        </is>
+      </c>
+      <c r="BE132" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>1673</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH132" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BK132" t="inlineStr"/>
+      <c r="BL132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="inlineStr">
+        <is>
+          <t>hY1c0809</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>28.06.2024 21:30</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Scheer J.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>AutoZone Park
+ (Memphis, TN)</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2 775</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>MoS88xdH</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Memphis</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>CWnNB64j</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>Phoenix Rising</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr"/>
+      <c r="X133" t="inlineStr"/>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr"/>
+      <c r="AD133" t="inlineStr"/>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AG133" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="AL133" t="inlineStr">
+        <is>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="AM133" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="AN133" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="AO133" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AP133" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AQ133" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="AT133" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="AU133" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AV133" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BA133" t="inlineStr">
+        <is>
+          <t>S2Oqee3l</t>
+        </is>
+      </c>
+      <c r="BB133" t="inlineStr">
+        <is>
+          <t>glass stephen</t>
+        </is>
+      </c>
+      <c r="BC133" t="inlineStr">
+        <is>
+          <t>McXMYtMJ</t>
+        </is>
+      </c>
+      <c r="BD133" t="inlineStr">
+        <is>
+          <t>stone danny</t>
+        </is>
+      </c>
+      <c r="BE133" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1673</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH133" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI133" t="inlineStr"/>
+      <c r="BJ133" t="inlineStr"/>
+      <c r="BK133" t="inlineStr"/>
+      <c r="BL133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="inlineStr">
+        <is>
+          <t>A9Ch1lo3</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>28.06.2024 20:30</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Flores G.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Patriots Point Soccer Complex
+ (Mount Pleasant, SC)</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>5 000</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>3 876</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>2wA8p3yn</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Charleston</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>OnB4oqMu</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr"/>
+      <c r="X134" t="inlineStr"/>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr"/>
+      <c r="AD134" t="inlineStr"/>
+      <c r="AE134" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF134" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG134" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AL134" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="AM134" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="AN134" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AP134" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ134" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="AT134" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AU134" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AV134" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BA134" t="inlineStr">
+        <is>
+          <t>zPVO4eiP</t>
+        </is>
+      </c>
+      <c r="BB134" t="inlineStr">
+        <is>
+          <t>pirmann ben</t>
+        </is>
+      </c>
+      <c r="BC134" t="inlineStr">
+        <is>
+          <t>0YXKhAXq</t>
+        </is>
+      </c>
+      <c r="BD134" t="inlineStr">
+        <is>
+          <t>bradford john</t>
+        </is>
+      </c>
+      <c r="BE134" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>1673</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH134" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BJ134" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BK134" t="inlineStr"/>
+      <c r="BL134" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
